--- a/Assets/Resources/Excel/Dialogues.xlsx
+++ b/Assets/Resources/Excel/Dialogues.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22586852-3116-4D42-9B43-EB73F5690B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{465A0775-4BBA-454B-8BC2-163394556699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
   <si>
     <t>CharacterTID</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Situation</t>
   </si>
   <si>
+    <t>RequiredLevel</t>
+  </si>
+  <si>
     <t>DialogID</t>
   </si>
   <si>
@@ -54,10 +57,22 @@
     <t>lobbyEnter</t>
   </si>
   <si>
-    <t>로비 씬에서의 대사 1</t>
-  </si>
-  <si>
-    <t>로비 씬에서의 대사 2</t>
+    <t>로비 씬에서의 대사 0-1</t>
+  </si>
+  <si>
+    <t>로비 씬에서의 대사 0-2</t>
+  </si>
+  <si>
+    <t>로비 씬에서의 대사 3-1</t>
+  </si>
+  <si>
+    <t>로비 씬에서의 대사 3-2</t>
+  </si>
+  <si>
+    <t>로비 씬에서의 대사 5-1</t>
+  </si>
+  <si>
+    <t>로비 씬에서의 대사 5-2</t>
   </si>
   <si>
     <t>storyOpen</t>
@@ -490,16 +505,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="6" max="6" width="23.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,362 +531,451 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>101</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>10101</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>10102</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>10103</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>10104</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>10101</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E6">
+        <v>10105</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D7">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>10102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
+      <c r="E7">
+        <v>10106</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
         <v>10111</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>101</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
         <v>10112</v>
       </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>101</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6">
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10">
         <v>10113</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>101</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
         <v>10114</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12">
         <v>10115</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9">
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13">
         <v>10121</v>
       </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>101</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10">
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14">
         <v>10122</v>
       </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11">
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>101</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
         <v>10131</v>
       </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>101</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12">
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16">
         <v>10132</v>
       </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>101</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13">
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17">
         <v>10141</v>
       </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>101</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14">
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18">
         <v>10142</v>
       </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>101</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19">
         <v>10151</v>
       </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16">
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20">
         <v>10152</v>
       </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17">
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21">
         <v>10161</v>
       </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>101</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18">
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22">
         <v>10162</v>
       </c>
-      <c r="E18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>101</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19">
+      <c r="F22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23">
         <v>10171</v>
       </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>101</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20">
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>101</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24">
         <v>10172</v>
       </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>101</v>
-      </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21">
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>101</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25">
         <v>10181</v>
       </c>
-      <c r="E21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>101</v>
-      </c>
-      <c r="B22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22">
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26">
         <v>10182</v>
       </c>
-      <c r="E22" t="s">
-        <v>35</v>
+      <c r="F26" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Excel/Dialogues.xlsx
+++ b/Assets/Resources/Excel/Dialogues.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30309"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{465A0775-4BBA-454B-8BC2-163394556699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBA29238-DF1A-40D6-88F1-A53100466808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="59">
   <si>
     <t>CharacterTID</t>
   </si>
@@ -57,22 +57,40 @@
     <t>lobbyEnter</t>
   </si>
   <si>
-    <t>로비 씬에서의 대사 0-1</t>
-  </si>
-  <si>
-    <t>로비 씬에서의 대사 0-2</t>
-  </si>
-  <si>
-    <t>로비 씬에서의 대사 3-1</t>
-  </si>
-  <si>
-    <t>로비 씬에서의 대사 3-2</t>
-  </si>
-  <si>
-    <t>로비 씬에서의 대사 5-1</t>
-  </si>
-  <si>
-    <t>로비 씬에서의 대사 5-2</t>
+    <t>아... 또 머리가 지끈거리네요. 제가... 방금 전까지 무슨 생각을 하고 있었죠, 관제사님?</t>
+  </si>
+  <si>
+    <t>제 이름은 유안... 임무는 잠수... 맞나요?</t>
+  </si>
+  <si>
+    <t>관제사님, 저를 놓치지 마세요. 이 어둠 속에서는 목소리마저 흩어져 버릴 것 같으니까요...</t>
+  </si>
+  <si>
+    <t>이제 관제사님의 목소리가 꽤 친숙하게 들려요. 든든한 느낌이에요.</t>
+  </si>
+  <si>
+    <t>현실의 하늘은 어떤가요? 이 어두운 심연 속에 있으면 가끔 궁금해져요.</t>
+  </si>
+  <si>
+    <t>저를 모니터링해주실 때, 머릿속이 조금 따뜻해지는 기분이 들어요.</t>
+  </si>
+  <si>
+    <t>관제사님이 없는 출격은 이제 생각도 하기 싫어. ...저, 제법 제멋대로가 되어버린 걸까요?</t>
+  </si>
+  <si>
+    <t>혹시 피곤하진 않아? 제 상태보다는 관제사님 건강이 더 걱정돼서 그래요.</t>
+  </si>
+  <si>
+    <t>무슨 일이 있어도 내 앵커가 되어주기로 한 약속, 잊으면 안 돼요? 믿고 있으니까.</t>
+  </si>
+  <si>
+    <t>이제 눈을 감아도 관제사님이 느껴져. 신기하지? 우리 정말 영혼까지 이어진 걸까.</t>
+  </si>
+  <si>
+    <t>잃어버린 기억을 다 되찾는다고 해도, 관제사님과 함께하는 지금 이 순간보다 소중하진 않을 거예요.</t>
+  </si>
+  <si>
+    <t>제 곁에 계속 있어 줘요. 오직 관제사님만이 저를 현실에 묶어두는 유일한 생명줄이니까요.</t>
   </si>
   <si>
     <t>storyOpen</t>
@@ -141,32 +159,73 @@
     <t>escapeSuccess</t>
   </si>
   <si>
-    <t>임무 성공 시 대사 1</t>
-  </si>
-  <si>
-    <t>임무 성공 시 대사 2</t>
+    <t>휴, 다행히 복귀했지만, 아직 머릿속이 복잡하네요...</t>
+  </si>
+  <si>
+    <t>성공한 건가요? 인도해 주셔서... 네, 감사합니다.</t>
+  </si>
+  <si>
+    <t>제대로 탈출해서 정말 다행이에요. 관제사님이 끝까지 목소리를 들려주신 덕분이에요!</t>
+  </si>
+  <si>
+    <t>돌아왔네요! 역시 관제사님이 열어준 탈출 지점은 신뢰할 수 있어요.</t>
+  </si>
+  <si>
+    <t>다녀왔어요! 하하, 관제사님 목소리를 들으니까 긴장이 싹 풀리는 거 있지?</t>
+  </si>
+  <si>
+    <t>무사히 탈출할 거라고 믿었어. 관제사님이 내 뒤에 든든하게 서 있으니까.</t>
+  </si>
+  <si>
+    <t>다녀왔어요, 관제사님. 밑바닥에서도 당신 빛이 보여서 금방 길을 찾았어요.</t>
+  </si>
+  <si>
+    <t>성공할 때마다 관제사님과 더 깊게 엮이는 기분이에요. ...이대로 계속 같이 있고 싶을 정도로.</t>
   </si>
   <si>
     <t>escapeFailed</t>
   </si>
   <si>
-    <t>임무 실패 시 대사 1</t>
-  </si>
-  <si>
-    <t>임무 실패 시 대사 2</t>
+    <t>으윽... 신호가 전부 끊겨서... 홀로 남겨진 기분이었어요. 아직도 몸이 떨려요</t>
+  </si>
+  <si>
+    <t>실패... 기억들이 산산조각 난 느낌이에요.</t>
+  </si>
+  <si>
+    <t>아쉬워라... 거의 다 왔었는데... 그래도 관제사님이 무사하셔서 다행이에요.</t>
+  </si>
+  <si>
+    <t>조금 무서웠지만... 관제사님이 계속 불러주신 덕에 정신을 차릴 수 있었어요.</t>
+  </si>
+  <si>
+    <t>너무 자책하지 마, 관제사님. 내 컨디션이 나빴던 거니까... 다음엔 꼭 같이 성공하자.</t>
+  </si>
+  <si>
+    <t>아야야... 조금 아프지만 괜찮아. 관제사님이야말로 너무 긴장하지 마요.</t>
+  </si>
+  <si>
+    <t>많이 놀랐죠? 괜찮아요. 연결이 잠시 끊겼을 뿐인데도, 당신 마음은 다 느껴졌는걸.</t>
+  </si>
+  <si>
+    <t>아쉽지만 괜찮아요. 다시 찾으러 가면 그만이니까.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
     </font>
   </fonts>
   <fills count="2">
@@ -189,8 +248,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -505,14 +570,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="6" max="6" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="92.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -549,9 +614,9 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10101</v>
-      </c>
-      <c r="F2" t="s">
+        <v>101001</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -569,7 +634,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10102</v>
+        <v>101002</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -586,12 +651,12 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>10103</v>
-      </c>
-      <c r="F4" t="s">
+        <v>101003</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -606,10 +671,10 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>10104</v>
+        <v>101004</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -626,10 +691,10 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>10105</v>
+        <v>101005</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -646,10 +711,10 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>10106</v>
+        <v>101006</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
@@ -663,13 +728,16 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>101007</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E8">
-        <v>10111</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -680,13 +748,16 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>10112</v>
+        <v>101008</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -697,13 +768,16 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>10113</v>
+        <v>101009</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -714,13 +788,16 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>10114</v>
+        <v>101010</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -731,13 +808,16 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
       </c>
       <c r="E12">
-        <v>10115</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
+        <v>101011</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -748,13 +828,16 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>10121</v>
+        <v>101012</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -768,10 +851,10 @@
         <v>20</v>
       </c>
       <c r="E14">
-        <v>10122</v>
+        <v>101101</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -782,13 +865,13 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E15">
-        <v>10131</v>
+        <v>101101</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -799,13 +882,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>101101</v>
+      </c>
+      <c r="F16" t="s">
         <v>23</v>
-      </c>
-      <c r="E16">
-        <v>10132</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -816,13 +899,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>10141</v>
+        <v>101101</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -833,13 +916,13 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>10142</v>
+        <v>101101</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -850,13 +933,13 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E19">
-        <v>10151</v>
+        <v>101201</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -867,13 +950,13 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E20">
-        <v>10152</v>
+        <v>101201</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -884,13 +967,13 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E21">
-        <v>10161</v>
+        <v>101301</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -901,13 +984,13 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E22">
-        <v>10162</v>
+        <v>101302</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -918,13 +1001,13 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E23">
-        <v>10171</v>
+        <v>101401</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -935,13 +1018,13 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E24">
-        <v>10172</v>
+        <v>101402</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -952,13 +1035,13 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E25">
-        <v>10181</v>
+        <v>101501</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -969,13 +1052,367 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26">
+        <v>101502</v>
+      </c>
+      <c r="F26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
         <v>38</v>
       </c>
-      <c r="E26">
-        <v>10182</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E27">
+        <v>101601</v>
+      </c>
+      <c r="F27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28">
+        <v>101602</v>
+      </c>
+      <c r="F28" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>101701</v>
+      </c>
+      <c r="F29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>101</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>101702</v>
+      </c>
+      <c r="F30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>101703</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>101</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>101704</v>
+      </c>
+      <c r="F32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>101705</v>
+      </c>
+      <c r="F33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>101706</v>
+      </c>
+      <c r="F34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>101707</v>
+      </c>
+      <c r="F35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>101708</v>
+      </c>
+      <c r="F36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>101801</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>101802</v>
+      </c>
+      <c r="F38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>101803</v>
+      </c>
+      <c r="F39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>101</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>101804</v>
+      </c>
+      <c r="F40" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>101</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>101805</v>
+      </c>
+      <c r="F41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>101806</v>
+      </c>
+      <c r="F42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>101</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>101807</v>
+      </c>
+      <c r="F43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>101</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>101808</v>
+      </c>
+      <c r="F44" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Excel/Dialogues.xlsx
+++ b/Assets/Resources/Excel/Dialogues.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30318"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBA29238-DF1A-40D6-88F1-A53100466808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A877490F-5480-4FE6-94F6-EDAF739DC088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="109">
   <si>
     <t>CharacterTID</t>
   </si>
@@ -96,19 +96,223 @@
     <t>storyOpen</t>
   </si>
   <si>
-    <t>심상 기록 대사 1-1</t>
-  </si>
-  <si>
-    <t>심상 기록 대사 1-2</t>
-  </si>
-  <si>
-    <t>심상 기록 대사 1-3</t>
-  </si>
-  <si>
-    <t>심상 기록 대사 1-4</t>
-  </si>
-  <si>
-    <t>심상 기록 대사 1-5</t>
+    <t>[유안]: 처음 뵙겠습니다, 관제사님. 오늘부로 전속 다이버로 배정된 유안입니다.</t>
+  </si>
+  <si>
+    <t>[관제사]: 반가워, 유안. 장비 피팅 상태는 어때? 조이는 곳이 있으면 바로 말해.</t>
+  </si>
+  <si>
+    <t>[유안]: 치수는 맞는데... 생각보다 무겁네요. 교복을 사물함에 넣어두고 이걸 입으니까 실감이 안 나요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 처음에는 다들 그래. 도시 내부에 진입하면 내가 주파수를 맞추고 계속 지원할 거야. 순서대로 하면 돼.</t>
+  </si>
+  <si>
+    <t>[유안]: ...대기실에서 다른 다이버가 초점 없이 멍하니 앉아 있는 걸 봤어요. 저도 저렇게 될 수 있는 건가요?</t>
+  </si>
+  <si>
+    <t>[관제사]: 무서운 게 당연해. 숨기지 않아도 돼. 공포 반응이 나오면 즉시 보고해. 그게 네 상태를 지키는 첫 번째 절차야.</t>
+  </si>
+  <si>
+    <t>[유안]: 절차요? 다른 관리자분들은 그냥 '잘 해' 라고만 하던데.</t>
+  </si>
+  <si>
+    <t>[관제사]: 난 좀 달라. 네 신호가 약해지면 임무보다 철수를 우선할 거야. 그리고 일정 간격으로 네 이름을 부를 거니까, 대답이 가능하면 해줘.</t>
+  </si>
+  <si>
+    <t>[유안]: 이름을요? ...왜요?</t>
+  </si>
+  <si>
+    <t>[관제사]: 도시 내부에서는 자기가 누구인지 흐려질 수 있어. 이름을 듣는 건 자기 자신을 붙잡는 가장 간단한 방법이야.</t>
+  </si>
+  <si>
+    <t>[유안]: ...그러면 저도 하나만 부탁해도 될까요? 제가 대답하지 못하더라도, 한 번만 더 이름을 불러주세요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 알겠어. 반드시 확인할게. 첫 출격, 잘 부탁해—유안.</t>
+  </si>
+  <si>
+    <t>[유안]: ...네. 들리네요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 유안, 몸은 괜찮아? 담요 가져올까? 이번 출격은 평소보다 오래 걸렸으니까.</t>
+  </si>
+  <si>
+    <t>[유안]: 괜찮아요. 따뜻한 차 마시니까 좀 살 것 같아요. ...그런데 관제사님, 하나 물어봐도 돼요?</t>
+  </si>
+  <si>
+    <t>[관제사]: 뭔데?</t>
+  </si>
+  <si>
+    <t>[유안]: 학교 다닐 때 매점에서 자주 사 먹던 빵 이름이 있었는데... 오늘 갑자기 떠올리려니까 안 나와요. 그게 원래 이런 건가요?</t>
+  </si>
+  <si>
+    <t>[관제사]: ......그럴 수 있어. 출격이 반복되면 오래된 일상 기억부터 흐려지는 경우가 있어.</t>
+  </si>
+  <si>
+    <t>[유안]: 그렇구나... 빵 이름 같은 건 괜찮은데, 솔직히 무서운 건 다른 거예요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 뭐가 무서워?</t>
+  </si>
+  <si>
+    <t>[유안]: 도시 내부에서 제가 어디까지 저인지 헷갈릴 때가 있어요. 그런데 관제사님이 제 이름을 부르면, 돌아갈 곳이 있다는 걸 알 수 있거든요. 그 목소리가 끊기면 어떡하나... 그게 제일 무서워요.</t>
+  </si>
+  <si>
+    <t>[관제사]: ......미안해. 내가 너를 계속 보내고 있으니까.</t>
+  </si>
+  <si>
+    <t>[유안]: 사과하지 마세요. 관제사님이 보내는 게 아니라 제가 가는 거예요. 그리고... 그 목소리가 지금은 제 닻이에요. 그게 없으면 흘러가 버릴 것 같으니까.</t>
+  </si>
+  <si>
+    <t>[관제사]: 그러면 계속 부를게. 네가 대답하지 못할 때도.</t>
+  </si>
+  <si>
+    <t>[유안]: 고마워요. ...언젠가는 저도 제 힘으로 돌아올 수 있으면 좋겠어요. 관제사님 목소리 없이도.</t>
+  </si>
+  <si>
+    <t>[관제사]: 유안. 이번 출격은 중단해야 해. 침식 중심부의 위험 지수가 임계점을 넘었어.</t>
+  </si>
+  <si>
+    <t>[유안]: 브리핑 자료 다 읽었어요. 중심부의 링크 주파수가 저하고 일치한다면서요? 다른 다이버로는 접근 자체가 안 되고.</t>
+  </si>
+  <si>
+    <t>[관제사]: 그렇다고 널 보낼 순 없어. 이 수준의 침식이면 네 기억뿐만 아니라 인격 구조 자체가 해체될 수 있어.</t>
+  </si>
+  <si>
+    <t>[유안]: 알아요. 내가 나를 잃어버리고... 관제사님을 잊게 될 수도 있다는 거.</t>
+  </si>
+  <si>
+    <t>[관제사]: 대체 작전을 올렸어. 시간을 벌면 다른 방법을 찾을 수 있어.</t>
+  </si>
+  <si>
+    <t>[유안]: 보고서에 적혀 있었어요. 이번 연결 창이 닫히면 중심부 접근이 장기간 불가능하다고. 그리고... 안쪽에 아직 반응하는 다이버 신호가 남아 있잖아요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 그건 잔류 신호일 수도 있어. 확인되지 않은 데이터야.</t>
+  </si>
+  <si>
+    <t>[유안]: 확인되지 않았으니까 가는 거예요. 누군가의 신호가 아직 남아 있는데 이 창이 닫히면 그건 진짜 끝이잖아요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 유안... 난 널 이 작전에 투입하는 승인서에 서명할 수 없어.</t>
+  </si>
+  <si>
+    <t>[유안]: 관제사님. 저는 지금까지 관제사님 지시를 따르며 여기까지 왔어요. 이번에는 제가 판단하고 싶어요.</t>
+  </si>
+  <si>
+    <t>[관제사]: ......잔류 신호 로그를 다시 볼게.</t>
+  </si>
+  <si>
+    <t>[관제사]: ...하나가 아니네. 최소 두 건의 반응이 간헐적으로 잡히고 있어. 네 말대로 아직 살아 있는 다이버가 있을 가능성은 있어.</t>
+  </si>
+  <si>
+    <t>[관제사]: 조건부로 승인할게. 하지만 철수 신호가 떨어지면 어떤 상황이든 즉시 돌아와. 이건 명령이야.</t>
+  </si>
+  <si>
+    <t>[유안]: 약속할게요. 그리고 관제사님도 하나만요.</t>
+  </si>
+  <si>
+    <t>[유안]: 제가 다 잊어버리더라도, 그때의 저를 억지로 되돌리지는 말아 주세요. 대신 제가 어떤 사람이었는지, 무엇을 선택했는지만 기록해 두세요.</t>
+  </si>
+  <si>
+    <t>[관제사]: ......기록할게. 네 선택을. 그걸 어떻게 받아들일지는 미래의 너에게 맡길게.</t>
+  </si>
+  <si>
+    <t>[유안]: 그리고 다시 만난 저에게 제 이름을 불러주세요. 믿을지는... 미래의 제가 다시 선택하게 해주세요.</t>
+  </si>
+  <si>
+    <t>[유안]: 다녀올게요, 관제사님.</t>
+  </si>
+  <si>
+    <t>[유안]: 관제사님. 기록... 봤어요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 그래.</t>
+  </si>
+  <si>
+    <t>[유안]: 이상하네요. 분명 제 목소리인데, 남의 이야기를 듣는 것 같았어요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 억지로 네 기억이라고 생각할 필요는 없어.</t>
+  </si>
+  <si>
+    <t>[유안]: 그럼 관제사님은요? 기록 속의 제가 돌아오길 기다린 건 아니에요?</t>
+  </si>
+  <si>
+    <t>[관제사]: ...기다렸던 적은 있어. 네가 기억을 잃기 전과 똑같아지길 바랐던 적도 있고.</t>
+  </si>
+  <si>
+    <t>[유안]: 지금은요?</t>
+  </si>
+  <si>
+    <t>[관제사]: 지금의 널 과거 기록에 맞추는 건, 또 한 번 널 잃는 일이라는 걸 알았어.</t>
+  </si>
+  <si>
+    <t>[유안]: 그런 말은 조금 반칙이네요.</t>
+  </si>
+  <si>
+    <t>[관제사]: 미안.</t>
+  </si>
+  <si>
+    <t>[유안]: 기록 속의 제가 왜 믿었는지는 아직 모르겠어요. 하지만 요즘의 관제사님은... 조금 알 것 같아요.</t>
+  </si>
+  <si>
+    <t>[유안]: 그러니까 이번에는 제가 정할게요. 다음 출격도 잘 부탁합니다, 관제사님.</t>
+  </si>
+  <si>
+    <t>escapeSuccess</t>
+  </si>
+  <si>
+    <t>휴, 다행히 복귀했지만, 아직 머릿속이 복잡하네요...</t>
+  </si>
+  <si>
+    <t>성공한 건가요? 인도해 주셔서... 네, 감사합니다.</t>
+  </si>
+  <si>
+    <t>제대로 탈출해서 정말 다행이에요. 관제사님이 끝까지 목소리를 들려주신 덕분이에요!</t>
+  </si>
+  <si>
+    <t>돌아왔네요! 역시 관제사님이 열어준 탈출 지점은 신뢰할 수 있어요.</t>
+  </si>
+  <si>
+    <t>다녀왔어요! 하하, 관제사님 목소리를 들으니까 긴장이 싹 풀리는 거 있지?</t>
+  </si>
+  <si>
+    <t>무사히 탈출할 거라고 믿었어. 관제사님이 내 뒤에 든든하게 서 있으니까.</t>
+  </si>
+  <si>
+    <t>다녀왔어요, 관제사님. 밑바닥에서도 당신 빛이 보여서 금방 길을 찾았어요.</t>
+  </si>
+  <si>
+    <t>성공할 때마다 관제사님과 더 깊게 엮이는 기분이에요. ...이대로 계속 같이 있고 싶을 정도로.</t>
+  </si>
+  <si>
+    <t>escapeFailed</t>
+  </si>
+  <si>
+    <t>으윽... 신호가 전부 끊겨서... 홀로 남겨진 기분이었어요. 아직도 몸이 떨려요</t>
+  </si>
+  <si>
+    <t>실패... 기억들이 산산조각 난 느낌이에요.</t>
+  </si>
+  <si>
+    <t>아쉬워라... 거의 다 왔었는데... 그래도 관제사님이 무사하셔서 다행이에요.</t>
+  </si>
+  <si>
+    <t>조금 무서웠지만... 관제사님이 계속 불러주신 덕에 정신을 차릴 수 있었어요.</t>
+  </si>
+  <si>
+    <t>너무 자책하지 마, 관제사님. 내 컨디션이 나빴던 거니까... 다음엔 꼭 같이 성공하자.</t>
+  </si>
+  <si>
+    <t>아야야... 조금 아프지만 괜찮아. 관제사님이야말로 너무 긴장하지 마요.</t>
+  </si>
+  <si>
+    <t>많이 놀랐죠? 괜찮아요. 연결이 잠시 끊겼을 뿐인데도, 당신 마음은 다 느껴졌는걸.</t>
+  </si>
+  <si>
+    <t>아쉽지만 괜찮아요. 다시 찾으러 가면 그만이니까.</t>
   </si>
   <si>
     <t>worldEnter</t>
@@ -154,60 +358,6 @@
   </si>
   <si>
     <t>소비 기물 획득 시 대사 2</t>
-  </si>
-  <si>
-    <t>escapeSuccess</t>
-  </si>
-  <si>
-    <t>휴, 다행히 복귀했지만, 아직 머릿속이 복잡하네요...</t>
-  </si>
-  <si>
-    <t>성공한 건가요? 인도해 주셔서... 네, 감사합니다.</t>
-  </si>
-  <si>
-    <t>제대로 탈출해서 정말 다행이에요. 관제사님이 끝까지 목소리를 들려주신 덕분이에요!</t>
-  </si>
-  <si>
-    <t>돌아왔네요! 역시 관제사님이 열어준 탈출 지점은 신뢰할 수 있어요.</t>
-  </si>
-  <si>
-    <t>다녀왔어요! 하하, 관제사님 목소리를 들으니까 긴장이 싹 풀리는 거 있지?</t>
-  </si>
-  <si>
-    <t>무사히 탈출할 거라고 믿었어. 관제사님이 내 뒤에 든든하게 서 있으니까.</t>
-  </si>
-  <si>
-    <t>다녀왔어요, 관제사님. 밑바닥에서도 당신 빛이 보여서 금방 길을 찾았어요.</t>
-  </si>
-  <si>
-    <t>성공할 때마다 관제사님과 더 깊게 엮이는 기분이에요. ...이대로 계속 같이 있고 싶을 정도로.</t>
-  </si>
-  <si>
-    <t>escapeFailed</t>
-  </si>
-  <si>
-    <t>으윽... 신호가 전부 끊겨서... 홀로 남겨진 기분이었어요. 아직도 몸이 떨려요</t>
-  </si>
-  <si>
-    <t>실패... 기억들이 산산조각 난 느낌이에요.</t>
-  </si>
-  <si>
-    <t>아쉬워라... 거의 다 왔었는데... 그래도 관제사님이 무사하셔서 다행이에요.</t>
-  </si>
-  <si>
-    <t>조금 무서웠지만... 관제사님이 계속 불러주신 덕에 정신을 차릴 수 있었어요.</t>
-  </si>
-  <si>
-    <t>너무 자책하지 마, 관제사님. 내 컨디션이 나빴던 거니까... 다음엔 꼭 같이 성공하자.</t>
-  </si>
-  <si>
-    <t>아야야... 조금 아프지만 괜찮아. 관제사님이야말로 너무 긴장하지 마요.</t>
-  </si>
-  <si>
-    <t>많이 놀랐죠? 괜찮아요. 연결이 잠시 끊겼을 뿐인데도, 당신 마음은 다 느껴졌는걸.</t>
-  </si>
-  <si>
-    <t>아쉽지만 괜찮아요. 다시 찾으러 가면 그만이니까.</t>
   </si>
 </sst>
 </file>
@@ -570,14 +720,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="6" max="6" width="92.875" customWidth="1"/>
+    <col min="6" max="6" width="119.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -850,6 +1000,9 @@
       <c r="C14" t="s">
         <v>20</v>
       </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
       <c r="E14">
         <v>101101</v>
       </c>
@@ -867,8 +1020,11 @@
       <c r="C15" t="s">
         <v>20</v>
       </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
       <c r="E15">
-        <v>101101</v>
+        <v>101102</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
@@ -884,8 +1040,11 @@
       <c r="C16" t="s">
         <v>20</v>
       </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
       <c r="E16">
-        <v>101101</v>
+        <v>101103</v>
       </c>
       <c r="F16" t="s">
         <v>23</v>
@@ -901,8 +1060,11 @@
       <c r="C17" t="s">
         <v>20</v>
       </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
       <c r="E17">
-        <v>101101</v>
+        <v>101104</v>
       </c>
       <c r="F17" t="s">
         <v>24</v>
@@ -918,8 +1080,11 @@
       <c r="C18" t="s">
         <v>20</v>
       </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
       <c r="E18">
-        <v>101101</v>
+        <v>101105</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -933,13 +1098,16 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>101106</v>
+      </c>
+      <c r="F19" t="s">
         <v>26</v>
-      </c>
-      <c r="E19">
-        <v>101201</v>
-      </c>
-      <c r="F19" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -950,13 +1118,16 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>101201</v>
+        <v>101107</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -967,13 +1138,16 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>101301</v>
+        <v>101108</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -984,13 +1158,16 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>101109</v>
+      </c>
+      <c r="F22" t="s">
         <v>29</v>
-      </c>
-      <c r="E22">
-        <v>101302</v>
-      </c>
-      <c r="F22" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1001,13 +1178,16 @@
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>101401</v>
+        <v>101110</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1018,13 +1198,16 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>101402</v>
+        <v>101111</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1035,13 +1218,16 @@
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>101501</v>
+        <v>101112</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1052,13 +1238,16 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>101502</v>
+        <v>101113</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1069,13 +1258,16 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>101601</v>
+        <v>101201</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1086,13 +1278,16 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>101602</v>
+        <v>101202</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1103,16 +1298,16 @@
         <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>101701</v>
+        <v>101203</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1123,16 +1318,16 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>101702</v>
+        <v>101204</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1143,16 +1338,16 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31">
-        <v>101703</v>
+        <v>101205</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1163,16 +1358,16 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32">
-        <v>101704</v>
+        <v>101206</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1183,16 +1378,16 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>101705</v>
+        <v>101207</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1203,16 +1398,16 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>101208</v>
+      </c>
+      <c r="F34" t="s">
         <v>41</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>101706</v>
-      </c>
-      <c r="F34" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1223,16 +1418,16 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>101707</v>
+        <v>101209</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1243,16 +1438,16 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>101708</v>
+        <v>101210</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1263,16 +1458,16 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>101801</v>
+        <v>101211</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1283,16 +1478,16 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>101802</v>
+        <v>101212</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1303,16 +1498,16 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>101803</v>
+        <v>101301</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1323,16 +1518,16 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>101804</v>
+        <v>101302</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1343,16 +1538,16 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41">
-        <v>101805</v>
+        <v>101303</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1363,16 +1558,16 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
       <c r="E42">
-        <v>101806</v>
+        <v>101304</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1383,16 +1578,16 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>101305</v>
+      </c>
+      <c r="F43" t="s">
         <v>50</v>
-      </c>
-      <c r="D43">
-        <v>4</v>
-      </c>
-      <c r="E43">
-        <v>101807</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1403,16 +1598,986 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>101306</v>
+      </c>
+      <c r="F44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>101307</v>
+      </c>
+      <c r="F45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>101</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>101308</v>
+      </c>
+      <c r="F46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>101</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>101309</v>
+      </c>
+      <c r="F47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>101</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>101310</v>
+      </c>
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>101311</v>
+      </c>
+      <c r="F49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>101</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>101312</v>
+      </c>
+      <c r="F50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>101</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>101313</v>
+      </c>
+      <c r="F51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>101</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>101314</v>
+      </c>
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53">
+        <v>101315</v>
+      </c>
+      <c r="F53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>101316</v>
+      </c>
+      <c r="F54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>101</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>101317</v>
+      </c>
+      <c r="F55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>101</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56">
+        <v>101318</v>
+      </c>
+      <c r="F56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>101</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57">
         <v>4</v>
       </c>
-      <c r="E44">
+      <c r="E57">
+        <v>101401</v>
+      </c>
+      <c r="F57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>101</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>101402</v>
+      </c>
+      <c r="F58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>101</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59">
+        <v>101403</v>
+      </c>
+      <c r="F59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>101</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
+        <v>101404</v>
+      </c>
+      <c r="F60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>101</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
+        <v>101405</v>
+      </c>
+      <c r="F61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>101</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>101406</v>
+      </c>
+      <c r="F62" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>101</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63">
+        <v>101407</v>
+      </c>
+      <c r="F63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>101</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>101408</v>
+      </c>
+      <c r="F64" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>101</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65">
+        <v>101409</v>
+      </c>
+      <c r="F65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>101</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>101410</v>
+      </c>
+      <c r="F66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>101</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>101411</v>
+      </c>
+      <c r="F67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>101</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>101412</v>
+      </c>
+      <c r="F68" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>101</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>101701</v>
+      </c>
+      <c r="F69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>101</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>101702</v>
+      </c>
+      <c r="F70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71">
+        <v>101703</v>
+      </c>
+      <c r="F71" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>101</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>101704</v>
+      </c>
+      <c r="F72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>101</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>101705</v>
+      </c>
+      <c r="F73" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>101</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+      <c r="E74">
+        <v>101706</v>
+      </c>
+      <c r="F74" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>101</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>76</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75">
+        <v>101707</v>
+      </c>
+      <c r="F75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>101</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76">
+        <v>101708</v>
+      </c>
+      <c r="F76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>101</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>101801</v>
+      </c>
+      <c r="F77" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>101</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>85</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>101802</v>
+      </c>
+      <c r="F78" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>101</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>101803</v>
+      </c>
+      <c r="F79" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>101</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80">
+        <v>101804</v>
+      </c>
+      <c r="F80" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>101</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>85</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81">
+        <v>101805</v>
+      </c>
+      <c r="F81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>101</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+      <c r="E82">
+        <v>101806</v>
+      </c>
+      <c r="F82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>101</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>101807</v>
+      </c>
+      <c r="F83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>101</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" t="s">
+        <v>85</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84">
         <v>101808</v>
       </c>
-      <c r="F44" t="s">
-        <v>58</v>
+      <c r="F84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>101</v>
+      </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" t="s">
+        <v>94</v>
+      </c>
+      <c r="E85">
+        <v>101901</v>
+      </c>
+      <c r="F85" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>101</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" t="s">
+        <v>94</v>
+      </c>
+      <c r="E86">
+        <v>101902</v>
+      </c>
+      <c r="F86" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>101</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" t="s">
+        <v>97</v>
+      </c>
+      <c r="E87">
+        <v>101903</v>
+      </c>
+      <c r="F87" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>101</v>
+      </c>
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="E88">
+        <v>101904</v>
+      </c>
+      <c r="F88" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>101</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
+      <c r="E89">
+        <v>101905</v>
+      </c>
+      <c r="F89" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>101</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>100</v>
+      </c>
+      <c r="E90">
+        <v>101906</v>
+      </c>
+      <c r="F90" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>101</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>103</v>
+      </c>
+      <c r="E91">
+        <v>101907</v>
+      </c>
+      <c r="F91" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>101</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92">
+        <v>101908</v>
+      </c>
+      <c r="F92" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>101</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>106</v>
+      </c>
+      <c r="E93">
+        <v>101909</v>
+      </c>
+      <c r="F93" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>106</v>
+      </c>
+      <c r="E94">
+        <v>101910</v>
+      </c>
+      <c r="F94" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
